--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260604.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260604.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>遠雄</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>72,239,000</t>
+          <t>36,460,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>36,460,000</t>
+          <t>8,550,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>遠雄</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>8,550,000</t>
+          <t>72,239,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>45,930,000</t>
+          <t>28,590,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>28,590,000</t>
+          <t>45,930,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>8,510,000</t>
+          <t>12,150,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>12,150,000</t>
+          <t>11,730,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>11,730,000</t>
+          <t>8,510,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
